--- a/data/trans_orig/KIDM_A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_A_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2007 (tasa de respuesta: 87,69%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2007 (tasa de respuesta: 87,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>29395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66303</t>
+          <t>66876</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21537</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25493</t>
+          <t>25505</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48757</t>
+          <t>48852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>22834</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44907</t>
+          <t>44899</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49650</t>
+          <t>49649</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69877</t>
+          <t>70465</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76360</t>
+          <t>76446</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79144</t>
+          <t>79301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>159288</t>
+          <t>159356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42934</t>
+          <t>42842</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55978</t>
+          <t>55678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101927</t>
+          <t>101605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107263</t>
+          <t>107319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34165</t>
+          <t>34200</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66349</t>
+          <t>65855</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>248707</t>
+          <t>249041</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>256289</t>
+          <t>256294</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>274633</t>
+          <t>274239</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>282333</t>
+          <t>282423</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>526378</t>
+          <t>526915</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>537468</t>
+          <t>537497</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2012 (tasa de respuesta: 90,72%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2012 (tasa de respuesta: 90,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32149</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63850</t>
+          <t>63088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26570</t>
+          <t>26423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61408</t>
+          <t>61097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39415</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25521</t>
+          <t>24489</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66941</t>
+          <t>66914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>15422</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71772</t>
+          <t>71101</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78314</t>
+          <t>78323</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85394</t>
+          <t>85396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>93169</t>
+          <t>92794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160370</t>
+          <t>159571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170045</t>
+          <t>169921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>797</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63047</t>
+          <t>62901</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59526</t>
+          <t>59043</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65445</t>
+          <t>65315</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125439</t>
+          <t>125298</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131958</t>
+          <t>131919</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16352</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30427</t>
+          <t>30477</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>34777</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49111</t>
+          <t>48946</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55248</t>
+          <t>55138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15940</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,49 +5441,49 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>10715</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>6543</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>16747</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
           <t>5,75%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>10715</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>6459</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>17138</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>29</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13857</t>
+          <t>13280</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28310</t>
+          <t>28088</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>261405</t>
+          <t>261858</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>271980</t>
+          <t>272144</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,47 +5554,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>94,42%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>98,12%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>280557</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>274525</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>284729</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>96,32%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>94,25%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>280557</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>274134</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>284813</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>96,32%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>94,12%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>540307</t>
+          <t>540529</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>554760</t>
+          <t>555337</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2016 (tasa de respuesta: 89,47%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2016 (tasa de respuesta: 89,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31318</t>
+          <t>31425</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62189</t>
+          <t>62845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43300</t>
+          <t>43625</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88509</t>
+          <t>88547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>21786</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32719</t>
+          <t>32249</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56503</t>
+          <t>56522</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>11238</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97596</t>
+          <t>97250</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103537</t>
+          <t>103528</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80326</t>
+          <t>80345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88211</t>
+          <t>88152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>181860</t>
+          <t>182207</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>190700</t>
+          <t>190747</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64597</t>
+          <t>65380</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132749</t>
+          <t>132917</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>17519</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>297052</t>
+          <t>298415</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>305023</t>
+          <t>305407</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>296383</t>
+          <t>296714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>305663</t>
+          <t>305414</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>598620</t>
+          <t>597954</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>609677</t>
+          <t>609304</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24711</t>
+          <t>24409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56716</t>
+          <t>56988</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23181</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37698</t>
+          <t>37519</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62951</t>
+          <t>63897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134995</t>
+          <t>135717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33503</t>
+          <t>33604</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94525</t>
+          <t>94187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>870</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29318</t>
+          <t>29437</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>35209</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59559</t>
+          <t>59382</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65497</t>
+          <t>65374</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>201507</t>
+          <t>201511</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207386</t>
+          <t>207403</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>259599</t>
+          <t>259133</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>266766</t>
+          <t>266676</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>463178</t>
+          <t>463401</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>472798</t>
+          <t>473130</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
